--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/VERMONT_2023.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/VERMONT_2023.xlsx
@@ -351,40 +351,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CHIAPAS</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACACOYAGUA</t>
+          <t>Acacoyagua</t>
         </is>
       </c>
       <c r="C2">
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALTAMIRANO</t>
+          <t>Altamirano</t>
         </is>
       </c>
       <c r="C3">
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COMITÁN DE DOMÍNGUEZ</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C4">
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COPAINALÁ</t>
+          <t>Copainalá</t>
         </is>
       </c>
       <c r="C5">
@@ -434,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ESCUINTLA</t>
+          <t>Escuintla</t>
         </is>
       </c>
       <c r="C6">
@@ -447,9 +467,14 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAS MARGARITAS</t>
+          <t>Las Margaritas</t>
         </is>
       </c>
       <c r="C7">
@@ -460,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MARAVILLA TENEJAPA</t>
+          <t>Maravilla Tenejapa</t>
         </is>
       </c>
       <c r="C8">
@@ -473,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SALTO DE AGUA</t>
+          <t>Salto De Agua</t>
         </is>
       </c>
       <c r="C9">
@@ -486,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SILTEPEC</t>
+          <t>Siltepec</t>
         </is>
       </c>
       <c r="C10">
@@ -499,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TEOPISCA</t>
+          <t>Teopisca</t>
         </is>
       </c>
       <c r="C11">
@@ -512,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C12">
@@ -527,12 +577,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TLÁHUAC</t>
+          <t>Tláhuac</t>
         </is>
       </c>
       <c r="C13">
@@ -543,9 +593,14 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C14">
@@ -558,12 +613,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COAHUILA DE ZARAGOZA</t>
+          <t>Coahuila De Zaragoza</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TORREÓN</t>
+          <t>Torreón</t>
         </is>
       </c>
       <c r="C15">
@@ -574,9 +629,14 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C16">
@@ -589,12 +649,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ESTADO DE MÉXICO</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHALCO</t>
+          <t>Chalco</t>
         </is>
       </c>
       <c r="C17">
@@ -605,9 +665,14 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C18">
@@ -620,12 +685,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IRAPUATO</t>
+          <t>Irapuato</t>
         </is>
       </c>
       <c r="C19">
@@ -636,9 +701,14 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LEÓN</t>
+          <t>León</t>
         </is>
       </c>
       <c r="C20">
@@ -649,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C21">
@@ -664,12 +739,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ATLIXTAC</t>
+          <t>Atlixtac</t>
         </is>
       </c>
       <c r="C22">
@@ -680,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAN LUIS ACATLÁN</t>
+          <t>San Luis Acatlán</t>
         </is>
       </c>
       <c r="C23">
@@ -693,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C24">
@@ -708,12 +793,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA MISIÓN</t>
+          <t>La Misión</t>
         </is>
       </c>
       <c r="C25">
@@ -724,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C26">
@@ -739,12 +829,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OAXACA</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAN ANDRÉS HUAXPALTEPEC</t>
+          <t>San Andrés Huaxpaltepec</t>
         </is>
       </c>
       <c r="C27">
@@ -755,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAN ANTONINO MONTE VERDE</t>
+          <t>San Antonino Monte Verde</t>
         </is>
       </c>
       <c r="C28">
@@ -768,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAN PEDRO MIXTEPEC -DTO. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C29">
@@ -781,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C30">
@@ -796,12 +901,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HUAQUECHULA</t>
+          <t>Huaquechula</t>
         </is>
       </c>
       <c r="C31">
@@ -812,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C32">
@@ -825,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TEZIUTLÁN</t>
+          <t>Teziutlán</t>
         </is>
       </c>
       <c r="C33">
@@ -838,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XICOTEPEC</t>
+          <t>Xicotepec</t>
         </is>
       </c>
       <c r="C34">
@@ -851,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XIUTETELCO</t>
+          <t>Xiutetelco</t>
         </is>
       </c>
       <c r="C35">
@@ -864,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C36">
@@ -879,12 +1009,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="C37">
@@ -895,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C38">
@@ -910,12 +1045,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUINTANA ROO</t>
+          <t>Quintana Roo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OTHÓN P. BLANCO</t>
+          <t>Othón P. Blanco</t>
         </is>
       </c>
       <c r="C39">
@@ -926,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C40">
@@ -941,12 +1081,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TIERRA NUEVA</t>
+          <t>Tierra Nueva</t>
         </is>
       </c>
       <c r="C41">
@@ -957,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>XILITLA</t>
+          <t>Xilitla</t>
         </is>
       </c>
       <c r="C42">
@@ -970,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C43">
@@ -985,12 +1135,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TABASCO</t>
+          <t>Tabasco</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BALANCÁN</t>
+          <t>Balancán</t>
         </is>
       </c>
       <c r="C44">
@@ -1001,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>Centro</t>
         </is>
       </c>
       <c r="C45">
@@ -1014,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COMALCALCO</t>
+          <t>Comalcalco</t>
         </is>
       </c>
       <c r="C46">
@@ -1027,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CÁRDENAS</t>
+          <t>Cárdenas</t>
         </is>
       </c>
       <c r="C47">
@@ -1040,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HUIMANGUILLO</t>
+          <t>Huimanguillo</t>
         </is>
       </c>
       <c r="C48">
@@ -1053,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C49">
@@ -1068,12 +1243,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TAMAULIPAS</t>
+          <t>Tamaulipas</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MATAMOROS</t>
+          <t>Matamoros</t>
         </is>
       </c>
       <c r="C50">
@@ -1084,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C51">
@@ -1099,12 +1279,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ALTOTONGA</t>
+          <t>Altotonga</t>
         </is>
       </c>
       <c r="C52">
@@ -1115,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ATZALAN</t>
+          <t>Atzalan</t>
         </is>
       </c>
       <c r="C53">
@@ -1128,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HUAYACOCOTLA</t>
+          <t>Huayacocotla</t>
         </is>
       </c>
       <c r="C54">
@@ -1141,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LAS CHOAPAS</t>
+          <t>Las Choapas</t>
         </is>
       </c>
       <c r="C55">
@@ -1154,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MARTÍNEZ DE LA TORRE</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C56">
@@ -1167,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MINATITLÁN</t>
+          <t>Minatitlán</t>
         </is>
       </c>
       <c r="C57">
@@ -1180,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NARANJOS AMATLÁN</t>
+          <t>Naranjos Amatlán</t>
         </is>
       </c>
       <c r="C58">
@@ -1193,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TLACOTALPAN</t>
+          <t>Tlacotalpan</t>
         </is>
       </c>
       <c r="C59">
@@ -1206,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TLALIXCOYAN</t>
+          <t>Tlalixcoyan</t>
         </is>
       </c>
       <c r="C60">
@@ -1219,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TLAQUILPA</t>
+          <t>Tlaquilpa</t>
         </is>
       </c>
       <c r="C61">
@@ -1232,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C62">
@@ -1247,7 +1477,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C63">
@@ -1255,41 +1485,6 @@
       </c>
       <c r="D63">
         <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 789,030</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Noviembre de 2024</t>
-        </is>
       </c>
     </row>
   </sheetData>
